--- a/data/trans_orig/P19C04-Clase-trans_orig.xlsx
+++ b/data/trans_orig/P19C04-Clase-trans_orig.xlsx
@@ -538,7 +538,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si el motivo por su última visita al dentista fue por la extracción de algún diente o muela en 2007</t>
+          <t>Población según si el motivo por su última visita al dentista fue por la extracción de algún diente o muela en 2007 (tasa de respuesta: 99,96%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>36326</t>
+          <t>36895</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>64405</t>
+          <t>63957</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>9,4%</t>
+          <t>9,55%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>16,67%</t>
+          <t>16,56%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>11717</t>
+          <t>11510</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>28592</t>
+          <t>28902</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>4,37%</t>
+          <t>4,29%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>10,66%</t>
+          <t>10,77%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>54403</t>
+          <t>53851</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>87455</t>
+          <t>86308</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>8,31%</t>
+          <t>8,23%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>13,36%</t>
+          <t>13,19%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>321897</t>
+          <t>322345</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>349976</t>
+          <t>349407</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>83,33%</t>
+          <t>83,44%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>90,6%</t>
+          <t>90,45%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>239695</t>
+          <t>239385</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>256570</t>
+          <t>256777</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>89,34%</t>
+          <t>89,23%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>95,63%</t>
+          <t>95,71%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>567135</t>
+          <t>568282</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>600187</t>
+          <t>600739</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>86,64%</t>
+          <t>86,81%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>91,69%</t>
+          <t>91,77%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>35075</t>
+          <t>35655</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>61374</t>
+          <t>60540</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>11,68%</t>
+          <t>11,88%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>20,44%</t>
+          <t>20,17%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>16585</t>
+          <t>16726</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>36986</t>
+          <t>38387</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>4,97%</t>
+          <t>5,01%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>11,09%</t>
+          <t>11,51%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>54733</t>
+          <t>57365</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>87890</t>
+          <t>91192</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>8,64%</t>
+          <t>9,05%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>13,87%</t>
+          <t>14,39%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>238831</t>
+          <t>239665</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>265130</t>
+          <t>264550</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>79,56%</t>
+          <t>79,83%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>88,32%</t>
+          <t>88,12%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>296579</t>
+          <t>295178</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>316980</t>
+          <t>316839</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>88,91%</t>
+          <t>88,49%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>95,03%</t>
+          <t>94,99%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>545880</t>
+          <t>542578</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>579037</t>
+          <t>576405</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>86,13%</t>
+          <t>85,61%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>91,36%</t>
+          <t>90,95%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>74183</t>
+          <t>76460</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>108159</t>
+          <t>110263</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>17,24%</t>
+          <t>17,77%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>25,14%</t>
+          <t>25,63%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>11948</t>
+          <t>12180</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>28434</t>
+          <t>27691</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>8,53%</t>
+          <t>8,7%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>20,3%</t>
+          <t>19,77%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>91020</t>
+          <t>92742</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>130367</t>
+          <t>131694</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>15,96%</t>
+          <t>16,26%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>22,86%</t>
+          <t>23,09%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>322108</t>
+          <t>320004</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>356084</t>
+          <t>353807</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>74,86%</t>
+          <t>74,37%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>82,76%</t>
+          <t>82,23%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>111634</t>
+          <t>112377</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>128120</t>
+          <t>127888</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>79,7%</t>
+          <t>80,23%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>91,47%</t>
+          <t>91,3%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>439968</t>
+          <t>438641</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>479315</t>
+          <t>477593</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>77,14%</t>
+          <t>76,91%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>84,04%</t>
+          <t>83,74%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>194416</t>
+          <t>194310</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>247436</t>
+          <t>246408</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>22,31%</t>
+          <t>22,3%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>28,39%</t>
+          <t>28,28%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>77578</t>
+          <t>79251</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>114070</t>
+          <t>115002</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>13,01%</t>
+          <t>13,29%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>19,13%</t>
+          <t>19,29%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>282812</t>
+          <t>286361</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>345011</t>
+          <t>348190</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>19,27%</t>
+          <t>19,51%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>23,51%</t>
+          <t>23,72%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>624018</t>
+          <t>625046</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>677038</t>
+          <t>677144</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>71,61%</t>
+          <t>71,72%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>77,69%</t>
+          <t>77,7%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>482179</t>
+          <t>481247</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>518671</t>
+          <t>516998</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>80,87%</t>
+          <t>80,71%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>86,99%</t>
+          <t>86,71%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1122691</t>
+          <t>1119512</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1184890</t>
+          <t>1181341</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>76,49%</t>
+          <t>76,28%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>80,73%</t>
+          <t>80,49%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>47462</t>
+          <t>47647</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>75067</t>
+          <t>76333</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>19,14%</t>
+          <t>19,22%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>30,28%</t>
+          <t>30,79%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>75028</t>
+          <t>74254</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>109157</t>
+          <t>110131</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>16,45%</t>
+          <t>16,28%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>23,93%</t>
+          <t>24,15%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>130395</t>
+          <t>130768</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>175838</t>
+          <t>174200</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>18,52%</t>
+          <t>18,57%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>24,98%</t>
+          <t>24,74%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>172860</t>
+          <t>171594</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>200465</t>
+          <t>200280</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>69,72%</t>
+          <t>69,21%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>80,86%</t>
+          <t>80,78%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>346923</t>
+          <t>345949</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>381052</t>
+          <t>381826</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>76,07%</t>
+          <t>75,85%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>83,55%</t>
+          <t>83,72%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>528169</t>
+          <t>529807</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>573612</t>
+          <t>573239</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>75,02%</t>
+          <t>75,26%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>81,48%</t>
+          <t>81,43%</t>
         </is>
       </c>
     </row>
@@ -2448,12 +2448,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>12840</t>
+          <t>12554</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>31231</t>
+          <t>30376</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2463,12 +2463,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>6,05%</t>
+          <t>5,91%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>14,72%</t>
+          <t>14,31%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2483,12 +2483,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>131956</t>
+          <t>133400</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>177667</t>
+          <t>176658</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2498,12 +2498,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>13,95%</t>
+          <t>14,11%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>18,79%</t>
+          <t>18,68%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2518,12 +2518,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>152743</t>
+          <t>152195</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>198838</t>
+          <t>199572</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2533,12 +2533,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>13,19%</t>
+          <t>13,14%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>17,17%</t>
+          <t>17,24%</t>
         </is>
       </c>
     </row>
@@ -2561,12 +2561,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>181002</t>
+          <t>181857</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>199393</t>
+          <t>199679</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2576,12 +2576,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>85,28%</t>
+          <t>85,69%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>93,95%</t>
+          <t>94,09%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2596,12 +2596,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>767949</t>
+          <t>768958</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>813660</t>
+          <t>812216</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2611,12 +2611,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>81,21%</t>
+          <t>81,32%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>86,05%</t>
+          <t>85,89%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2631,12 +2631,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>959011</t>
+          <t>958277</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>1005106</t>
+          <t>1005654</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2646,12 +2646,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>82,83%</t>
+          <t>82,76%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>86,81%</t>
+          <t>86,86%</t>
         </is>
       </c>
     </row>
@@ -2791,12 +2791,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>448647</t>
+          <t>449655</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>528703</t>
+          <t>530314</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2806,12 +2806,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>18,32%</t>
+          <t>18,37%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>21,59%</t>
+          <t>21,66%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>368158</t>
+          <t>363243</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>440775</t>
+          <t>436091</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2841,12 +2841,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>13,44%</t>
+          <t>13,26%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>16,09%</t>
+          <t>15,92%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>838187</t>
+          <t>838981</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>944199</t>
+          <t>952127</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2876,12 +2876,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>16,16%</t>
+          <t>16,17%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>18,2%</t>
+          <t>18,35%</t>
         </is>
       </c>
     </row>
@@ -2904,12 +2904,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>1919685</t>
+          <t>1918074</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>1999741</t>
+          <t>1998733</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>78,41%</t>
+          <t>78,34%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>81,68%</t>
+          <t>81,63%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2939,12 +2939,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>2299089</t>
+          <t>2303773</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>2371706</t>
+          <t>2376621</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2954,12 +2954,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>83,91%</t>
+          <t>84,08%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>86,56%</t>
+          <t>86,74%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2974,12 +2974,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>4244053</t>
+          <t>4236125</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>4350065</t>
+          <t>4349271</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2989,12 +2989,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>81,8%</t>
+          <t>81,65%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>83,84%</t>
+          <t>83,83%</t>
         </is>
       </c>
     </row>
@@ -3173,7 +3173,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si el motivo por su última visita al dentista fue por la extracción de algún diente o muela en 2012</t>
+          <t>Población según si el motivo por su última visita al dentista fue por la extracción de algún diente o muela en 2012 (tasa de respuesta: 99,82%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3368,12 +3368,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>40664</t>
+          <t>40740</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>69878</t>
+          <t>71399</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3383,12 +3383,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>10,29%</t>
+          <t>10,3%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>17,68%</t>
+          <t>18,06%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3403,12 +3403,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>20652</t>
+          <t>21410</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>43231</t>
+          <t>44333</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3418,12 +3418,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>7,03%</t>
+          <t>7,28%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>14,71%</t>
+          <t>15,08%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3438,12 +3438,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>66575</t>
+          <t>67515</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>103647</t>
+          <t>104549</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3453,12 +3453,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>9,66%</t>
+          <t>9,79%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>15,04%</t>
+          <t>15,17%</t>
         </is>
       </c>
     </row>
@@ -3481,12 +3481,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>325466</t>
+          <t>323945</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>354680</t>
+          <t>354604</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3496,12 +3496,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>82,32%</t>
+          <t>81,94%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>89,71%</t>
+          <t>89,7%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3516,12 +3516,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>250723</t>
+          <t>249621</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>273302</t>
+          <t>272544</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3531,12 +3531,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>85,29%</t>
+          <t>84,92%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>92,97%</t>
+          <t>92,72%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3551,12 +3551,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>585652</t>
+          <t>584750</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>622724</t>
+          <t>621784</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3566,12 +3566,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>84,96%</t>
+          <t>84,83%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>90,34%</t>
+          <t>90,21%</t>
         </is>
       </c>
     </row>
@@ -3711,12 +3711,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>42710</t>
+          <t>43593</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>71588</t>
+          <t>74484</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3726,12 +3726,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>11,13%</t>
+          <t>11,36%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>18,66%</t>
+          <t>19,41%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3746,12 +3746,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>23140</t>
+          <t>23245</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>45412</t>
+          <t>45811</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3761,12 +3761,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>7,38%</t>
+          <t>7,41%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>14,49%</t>
+          <t>14,61%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3781,12 +3781,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>71082</t>
+          <t>72322</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>110843</t>
+          <t>110812</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3796,12 +3796,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>10,19%</t>
+          <t>10,37%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>15,9%</t>
+          <t>15,89%</t>
         </is>
       </c>
     </row>
@@ -3824,12 +3824,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>312136</t>
+          <t>309240</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>341014</t>
+          <t>340131</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3839,12 +3839,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>81,34%</t>
+          <t>80,59%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>88,87%</t>
+          <t>88,64%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3859,12 +3859,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>268089</t>
+          <t>267690</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>290361</t>
+          <t>290256</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3874,12 +3874,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>85,51%</t>
+          <t>85,39%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>92,62%</t>
+          <t>92,59%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3894,12 +3894,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>586382</t>
+          <t>586413</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>626143</t>
+          <t>624903</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3909,12 +3909,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>84,1%</t>
+          <t>84,11%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>89,81%</t>
+          <t>89,63%</t>
         </is>
       </c>
     </row>
@@ -4054,12 +4054,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>120872</t>
+          <t>121322</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>162222</t>
+          <t>162313</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4069,12 +4069,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>22,57%</t>
+          <t>22,66%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>30,29%</t>
+          <t>30,31%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4089,12 +4089,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>17270</t>
+          <t>18126</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>37380</t>
+          <t>38586</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4104,12 +4104,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>7,21%</t>
+          <t>7,56%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>15,6%</t>
+          <t>16,1%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4124,12 +4124,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>145293</t>
+          <t>143651</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>192056</t>
+          <t>190546</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4139,12 +4139,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>18,74%</t>
+          <t>18,53%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>24,78%</t>
+          <t>24,58%</t>
         </is>
       </c>
     </row>
@@ -4167,12 +4167,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>373266</t>
+          <t>373175</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>414616</t>
+          <t>414166</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4182,12 +4182,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>69,71%</t>
+          <t>69,69%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>77,43%</t>
+          <t>77,34%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4202,12 +4202,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>202258</t>
+          <t>201052</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>222368</t>
+          <t>221512</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4217,12 +4217,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>84,4%</t>
+          <t>83,9%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>92,79%</t>
+          <t>92,44%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4237,12 +4237,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>583069</t>
+          <t>584579</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>629832</t>
+          <t>631474</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4252,12 +4252,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>75,22%</t>
+          <t>75,42%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>81,26%</t>
+          <t>81,47%</t>
         </is>
       </c>
     </row>
@@ -4397,12 +4397,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>282939</t>
+          <t>284292</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>346259</t>
+          <t>346455</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4412,12 +4412,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>29,09%</t>
+          <t>29,23%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>35,6%</t>
+          <t>35,62%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4432,12 +4432,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>88925</t>
+          <t>88548</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>130299</t>
+          <t>128259</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4447,12 +4447,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>12,72%</t>
+          <t>12,67%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>18,64%</t>
+          <t>18,35%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4467,12 +4467,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>387539</t>
+          <t>385587</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>459678</t>
+          <t>460639</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4482,12 +4482,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>23,18%</t>
+          <t>23,07%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>27,5%</t>
+          <t>27,56%</t>
         </is>
       </c>
     </row>
@@ -4510,12 +4510,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>626470</t>
+          <t>626274</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>689790</t>
+          <t>688437</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4525,12 +4525,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>64,4%</t>
+          <t>64,38%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>70,91%</t>
+          <t>70,77%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4545,12 +4545,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>568628</t>
+          <t>570668</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>610002</t>
+          <t>610379</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4560,12 +4560,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>81,36%</t>
+          <t>81,65%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>87,28%</t>
+          <t>87,33%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4580,12 +4580,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1211978</t>
+          <t>1211017</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1284117</t>
+          <t>1286069</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4595,12 +4595,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>72,5%</t>
+          <t>72,44%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>76,82%</t>
+          <t>76,93%</t>
         </is>
       </c>
     </row>
@@ -4740,12 +4740,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>115422</t>
+          <t>117077</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>153519</t>
+          <t>155872</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4755,12 +4755,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>28,62%</t>
+          <t>29,03%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>38,06%</t>
+          <t>38,65%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4775,12 +4775,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>136952</t>
+          <t>140111</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>182829</t>
+          <t>184568</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4790,12 +4790,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>20,48%</t>
+          <t>20,95%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>27,34%</t>
+          <t>27,6%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4810,12 +4810,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>266926</t>
+          <t>269972</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>326869</t>
+          <t>326092</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4825,12 +4825,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>24,9%</t>
+          <t>25,18%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>30,49%</t>
+          <t>30,42%</t>
         </is>
       </c>
     </row>
@@ -4853,12 +4853,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>249793</t>
+          <t>247440</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>287890</t>
+          <t>286235</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4868,12 +4868,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>61,94%</t>
+          <t>61,35%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>71,38%</t>
+          <t>70,97%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4888,12 +4888,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>485930</t>
+          <t>484191</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>531807</t>
+          <t>528648</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4903,12 +4903,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>72,66%</t>
+          <t>72,4%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>79,52%</t>
+          <t>79,05%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4923,12 +4923,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>745202</t>
+          <t>745979</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>805145</t>
+          <t>802099</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4938,12 +4938,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>69,51%</t>
+          <t>69,58%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>75,1%</t>
+          <t>74,82%</t>
         </is>
       </c>
     </row>
@@ -5083,12 +5083,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>13747</t>
+          <t>13505</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>31581</t>
+          <t>30489</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5098,12 +5098,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>6,21%</t>
+          <t>6,11%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>14,28%</t>
+          <t>13,78%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5118,12 +5118,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>166992</t>
+          <t>168929</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>216320</t>
+          <t>217917</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5133,12 +5133,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>18,03%</t>
+          <t>18,24%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>23,35%</t>
+          <t>23,52%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5153,12 +5153,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>186616</t>
+          <t>190138</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>242580</t>
+          <t>239873</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5168,12 +5168,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>16,26%</t>
+          <t>16,57%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>21,14%</t>
+          <t>20,9%</t>
         </is>
       </c>
     </row>
@@ -5196,12 +5196,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>189622</t>
+          <t>190714</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>207456</t>
+          <t>207698</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5211,12 +5211,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>85,72%</t>
+          <t>86,22%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>93,79%</t>
+          <t>93,89%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5231,12 +5231,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>710057</t>
+          <t>708460</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>759385</t>
+          <t>757448</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5246,12 +5246,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>76,65%</t>
+          <t>76,48%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>81,97%</t>
+          <t>81,76%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5266,12 +5266,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>905000</t>
+          <t>907707</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>960964</t>
+          <t>957442</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5281,12 +5281,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>78,86%</t>
+          <t>79,1%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>83,74%</t>
+          <t>83,43%</t>
         </is>
       </c>
     </row>
@@ -5426,12 +5426,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>673432</t>
+          <t>671919</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>768474</t>
+          <t>771843</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5441,12 +5441,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>23,13%</t>
+          <t>23,08%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>26,39%</t>
+          <t>26,51%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5461,12 +5461,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>509779</t>
+          <t>509463</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>603101</t>
+          <t>594915</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5476,12 +5476,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>16,23%</t>
+          <t>16,22%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>19,2%</t>
+          <t>18,94%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5496,12 +5496,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>1201974</t>
+          <t>1210570</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>1338228</t>
+          <t>1337341</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5511,12 +5511,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>19,86%</t>
+          <t>20,0%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>22,11%</t>
+          <t>22,09%</t>
         </is>
       </c>
     </row>
@@ -5539,12 +5539,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>2143326</t>
+          <t>2139957</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>2238368</t>
+          <t>2239881</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -5554,12 +5554,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>73,61%</t>
+          <t>73,49%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>76,87%</t>
+          <t>76,92%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -5574,12 +5574,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>2538055</t>
+          <t>2546241</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>2631377</t>
+          <t>2631693</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -5589,12 +5589,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>80,8%</t>
+          <t>81,06%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>83,77%</t>
+          <t>83,78%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -5609,12 +5609,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>4714728</t>
+          <t>4715615</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>4850982</t>
+          <t>4842386</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -5624,12 +5624,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>77,89%</t>
+          <t>77,91%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>80,14%</t>
+          <t>80,0%</t>
         </is>
       </c>
     </row>
@@ -5808,7 +5808,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si el motivo por su última visita al dentista fue por la extracción de algún diente o muela en 2016</t>
+          <t>Población según si el motivo por su última visita al dentista fue por la extracción de algún diente o muela en 2016 (tasa de respuesta: 99,98%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -6003,12 +6003,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>24736</t>
+          <t>24580</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>47851</t>
+          <t>47609</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6018,12 +6018,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>6,38%</t>
+          <t>6,34%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>12,34%</t>
+          <t>12,28%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6038,12 +6038,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>15791</t>
+          <t>16306</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>34953</t>
+          <t>34792</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6053,12 +6053,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>5,0%</t>
+          <t>5,16%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>11,07%</t>
+          <t>11,02%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6073,12 +6073,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>45369</t>
+          <t>43896</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>76023</t>
+          <t>74755</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6088,12 +6088,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>6,45%</t>
+          <t>6,24%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>10,81%</t>
+          <t>10,63%</t>
         </is>
       </c>
     </row>
@@ -6116,12 +6116,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>339763</t>
+          <t>340005</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>362878</t>
+          <t>363034</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -6131,12 +6131,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>87,66%</t>
+          <t>87,72%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>93,62%</t>
+          <t>93,66%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6151,12 +6151,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>280863</t>
+          <t>281024</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>300025</t>
+          <t>299510</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -6166,12 +6166,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>88,93%</t>
+          <t>88,98%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>95,0%</t>
+          <t>94,84%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6186,12 +6186,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>627407</t>
+          <t>628675</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>658061</t>
+          <t>659534</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -6201,12 +6201,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>89,19%</t>
+          <t>89,37%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>93,55%</t>
+          <t>93,76%</t>
         </is>
       </c>
     </row>
@@ -6346,12 +6346,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>28967</t>
+          <t>28942</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>53260</t>
+          <t>54499</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -6361,12 +6361,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>9,15%</t>
+          <t>9,14%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>16,82%</t>
+          <t>17,21%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -6381,12 +6381,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>12100</t>
+          <t>11523</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>30847</t>
+          <t>29846</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -6396,12 +6396,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>3,63%</t>
+          <t>3,45%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>9,25%</t>
+          <t>8,95%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6416,12 +6416,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>46433</t>
+          <t>45438</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>77608</t>
+          <t>77299</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -6431,12 +6431,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>7,14%</t>
+          <t>6,99%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>11,94%</t>
+          <t>11,89%</t>
         </is>
       </c>
     </row>
@@ -6459,12 +6459,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>263398</t>
+          <t>262159</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>287691</t>
+          <t>287716</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -6474,12 +6474,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>83,18%</t>
+          <t>82,79%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>90,85%</t>
+          <t>90,86%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -6494,12 +6494,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>302728</t>
+          <t>303729</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>321475</t>
+          <t>322052</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -6509,12 +6509,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>90,75%</t>
+          <t>91,05%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>96,37%</t>
+          <t>96,55%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -6529,12 +6529,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>572624</t>
+          <t>572933</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>603799</t>
+          <t>604794</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -6544,12 +6544,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>88,06%</t>
+          <t>88,11%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>92,86%</t>
+          <t>93,01%</t>
         </is>
       </c>
     </row>
@@ -6689,12 +6689,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>60110</t>
+          <t>58895</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>89257</t>
+          <t>89887</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -6704,12 +6704,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>14,83%</t>
+          <t>14,53%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>22,03%</t>
+          <t>22,18%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6724,12 +6724,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>13519</t>
+          <t>13876</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>32460</t>
+          <t>32739</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -6739,12 +6739,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>9,7%</t>
+          <t>9,95%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>23,28%</t>
+          <t>23,48%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6759,12 +6759,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>78900</t>
+          <t>78647</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>115571</t>
+          <t>114083</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -6774,12 +6774,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>14,49%</t>
+          <t>14,44%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>21,22%</t>
+          <t>20,95%</t>
         </is>
       </c>
     </row>
@@ -6802,12 +6802,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>315954</t>
+          <t>315324</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>345101</t>
+          <t>346316</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -6817,12 +6817,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>77,97%</t>
+          <t>77,82%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>85,17%</t>
+          <t>85,47%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -6837,12 +6837,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>106961</t>
+          <t>106682</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>125902</t>
+          <t>125545</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -6852,12 +6852,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>76,72%</t>
+          <t>76,52%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>90,3%</t>
+          <t>90,05%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -6872,12 +6872,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>429062</t>
+          <t>430550</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>465733</t>
+          <t>465986</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -6887,12 +6887,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>78,78%</t>
+          <t>79,05%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>85,51%</t>
+          <t>85,56%</t>
         </is>
       </c>
     </row>
@@ -7032,12 +7032,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>160729</t>
+          <t>163704</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>214931</t>
+          <t>212217</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7047,12 +7047,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>18,27%</t>
+          <t>18,61%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>24,44%</t>
+          <t>24,13%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7067,12 +7067,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>69327</t>
+          <t>68099</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>105433</t>
+          <t>103746</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7082,12 +7082,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>10,15%</t>
+          <t>9,97%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>15,44%</t>
+          <t>15,19%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7102,12 +7102,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>244165</t>
+          <t>242213</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>303418</t>
+          <t>305247</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7117,12 +7117,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>15,63%</t>
+          <t>15,5%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>19,42%</t>
+          <t>19,54%</t>
         </is>
       </c>
     </row>
@@ -7145,12 +7145,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>664574</t>
+          <t>667288</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>718776</t>
+          <t>715801</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7160,12 +7160,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>75,56%</t>
+          <t>75,87%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>81,73%</t>
+          <t>81,39%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7180,12 +7180,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>577503</t>
+          <t>579190</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>613609</t>
+          <t>614837</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7195,12 +7195,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>84,56%</t>
+          <t>84,81%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>89,85%</t>
+          <t>90,03%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7215,12 +7215,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1259023</t>
+          <t>1257194</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1318276</t>
+          <t>1320228</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7230,12 +7230,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>80,58%</t>
+          <t>80,46%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>84,37%</t>
+          <t>84,5%</t>
         </is>
       </c>
     </row>
@@ -7375,12 +7375,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>99268</t>
+          <t>99276</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>136944</t>
+          <t>138041</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -7395,7 +7395,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>32,21%</t>
+          <t>32,47%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7410,12 +7410,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>70080</t>
+          <t>70026</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>103639</t>
+          <t>106544</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -7425,12 +7425,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>12,57%</t>
+          <t>12,56%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>18,59%</t>
+          <t>19,11%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -7445,12 +7445,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>178706</t>
+          <t>179105</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>233363</t>
+          <t>231259</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -7460,12 +7460,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>18,19%</t>
+          <t>18,23%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>23,75%</t>
+          <t>23,53%</t>
         </is>
       </c>
     </row>
@@ -7488,12 +7488,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>288225</t>
+          <t>287128</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>325901</t>
+          <t>325893</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -7503,7 +7503,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>67,79%</t>
+          <t>67,53%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -7523,12 +7523,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>453842</t>
+          <t>450937</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>487401</t>
+          <t>487455</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -7538,12 +7538,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>81,41%</t>
+          <t>80,89%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>87,43%</t>
+          <t>87,44%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -7558,12 +7558,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>749287</t>
+          <t>751391</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>803944</t>
+          <t>803545</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -7573,12 +7573,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>76,25%</t>
+          <t>76,47%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>81,81%</t>
+          <t>81,77%</t>
         </is>
       </c>
     </row>
@@ -7718,12 +7718,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>14860</t>
+          <t>15078</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>32605</t>
+          <t>32664</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -7733,12 +7733,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>6,15%</t>
+          <t>6,24%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>13,5%</t>
+          <t>13,52%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -7753,12 +7753,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>113885</t>
+          <t>115360</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>160723</t>
+          <t>160839</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -7768,12 +7768,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>13,8%</t>
+          <t>13,98%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>19,47%</t>
+          <t>19,49%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -7788,12 +7788,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>135223</t>
+          <t>134473</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>182712</t>
+          <t>182716</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -7803,7 +7803,7 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>12,68%</t>
+          <t>12,6%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
@@ -7831,12 +7831,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>208943</t>
+          <t>208884</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>226688</t>
+          <t>226470</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -7846,12 +7846,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>86,5%</t>
+          <t>86,48%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>93,85%</t>
+          <t>93,76%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -7866,12 +7866,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>664566</t>
+          <t>664450</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>711404</t>
+          <t>709929</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -7881,12 +7881,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>80,53%</t>
+          <t>80,51%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>86,2%</t>
+          <t>86,02%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -7901,12 +7901,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>884125</t>
+          <t>884121</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>931614</t>
+          <t>932364</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -7921,7 +7921,7 @@
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>87,32%</t>
+          <t>87,4%</t>
         </is>
       </c>
     </row>
@@ -8061,12 +8061,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>434163</t>
+          <t>436941</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>514160</t>
+          <t>515877</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -8076,12 +8076,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>16,35%</t>
+          <t>16,45%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>19,36%</t>
+          <t>19,43%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -8096,12 +8096,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>338231</t>
+          <t>337750</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>410445</t>
+          <t>413760</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -8111,12 +8111,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>11,85%</t>
+          <t>11,83%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>14,38%</t>
+          <t>14,49%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -8131,12 +8131,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>794422</t>
+          <t>795535</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>908645</t>
+          <t>906355</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -8146,12 +8146,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>14,42%</t>
+          <t>14,44%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>16,49%</t>
+          <t>16,45%</t>
         </is>
       </c>
     </row>
@@ -8174,12 +8174,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>2141545</t>
+          <t>2139828</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>2221542</t>
+          <t>2218764</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -8189,12 +8189,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>80,64%</t>
+          <t>80,57%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>83,65%</t>
+          <t>83,55%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -8209,12 +8209,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>2444073</t>
+          <t>2440758</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>2516287</t>
+          <t>2516768</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -8224,12 +8224,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>85,62%</t>
+          <t>85,51%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>88,15%</t>
+          <t>88,17%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -8244,12 +8244,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>4601578</t>
+          <t>4603868</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>4715801</t>
+          <t>4714688</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -8259,12 +8259,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>83,51%</t>
+          <t>83,55%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>85,58%</t>
+          <t>85,56%</t>
         </is>
       </c>
     </row>
@@ -8443,7 +8443,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si el motivo por su última visita al dentista fue por la extracción de algún diente o muela en 2023</t>
+          <t>Población según si el motivo por su última visita al dentista fue por la extracción de algún diente o muela en 2023 (tasa de respuesta: 99,53%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -8638,12 +8638,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>31752</t>
+          <t>30329</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>55576</t>
+          <t>54686</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -8653,12 +8653,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>6,37%</t>
+          <t>6,08%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>11,15%</t>
+          <t>10,97%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -8673,12 +8673,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>14256</t>
+          <t>14373</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>28165</t>
+          <t>28515</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -8688,12 +8688,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>3,23%</t>
+          <t>3,26%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>6,39%</t>
+          <t>6,47%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -8708,12 +8708,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>50927</t>
+          <t>51039</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>78835</t>
+          <t>77793</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -8723,12 +8723,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>5,42%</t>
+          <t>5,43%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>8,39%</t>
+          <t>8,28%</t>
         </is>
       </c>
     </row>
@@ -8751,12 +8751,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>442906</t>
+          <t>443796</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>466730</t>
+          <t>468153</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -8766,12 +8766,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>88,85%</t>
+          <t>89,03%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>93,63%</t>
+          <t>93,92%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -8786,12 +8786,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>412760</t>
+          <t>412410</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>426669</t>
+          <t>426552</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -8801,12 +8801,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>93,61%</t>
+          <t>93,53%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>96,77%</t>
+          <t>96,74%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -8821,12 +8821,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>860572</t>
+          <t>861614</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>888480</t>
+          <t>888368</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -8836,12 +8836,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>91,61%</t>
+          <t>91,72%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>94,58%</t>
+          <t>94,57%</t>
         </is>
       </c>
     </row>
@@ -8981,12 +8981,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>34416</t>
+          <t>33948</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>60008</t>
+          <t>60009</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -8996,7 +8996,7 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>7,67%</t>
+          <t>7,57%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
@@ -9016,12 +9016,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>15223</t>
+          <t>15089</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>30999</t>
+          <t>30977</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -9031,12 +9031,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>4,03%</t>
+          <t>4,0%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>8,21%</t>
+          <t>8,2%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -9051,12 +9051,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>55028</t>
+          <t>54321</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>83481</t>
+          <t>84113</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -9066,12 +9066,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>6,66%</t>
+          <t>6,58%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>10,11%</t>
+          <t>10,18%</t>
         </is>
       </c>
     </row>
@@ -9094,12 +9094,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>388410</t>
+          <t>388409</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>414002</t>
+          <t>414470</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -9114,7 +9114,7 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>92,33%</t>
+          <t>92,43%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -9129,12 +9129,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>346607</t>
+          <t>346629</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>362383</t>
+          <t>362517</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -9144,12 +9144,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>91,79%</t>
+          <t>91,8%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>95,97%</t>
+          <t>96,0%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -9164,12 +9164,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>742542</t>
+          <t>741910</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>770995</t>
+          <t>771702</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -9179,12 +9179,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>89,89%</t>
+          <t>89,82%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>93,34%</t>
+          <t>93,42%</t>
         </is>
       </c>
     </row>
@@ -9324,12 +9324,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>20865</t>
+          <t>22701</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>105263</t>
+          <t>106188</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -9339,12 +9339,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>3,16%</t>
+          <t>3,44%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>15,93%</t>
+          <t>16,07%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -9359,12 +9359,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>11944</t>
+          <t>11492</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>23961</t>
+          <t>24481</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -9374,12 +9374,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>7,24%</t>
+          <t>6,97%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>14,52%</t>
+          <t>14,84%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -9394,12 +9394,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>38098</t>
+          <t>31685</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>120131</t>
+          <t>120573</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -9409,12 +9409,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>4,61%</t>
+          <t>3,84%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>14,55%</t>
+          <t>14,6%</t>
         </is>
       </c>
     </row>
@@ -9437,12 +9437,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>555466</t>
+          <t>554541</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>639864</t>
+          <t>638028</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -9452,12 +9452,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>84,07%</t>
+          <t>83,93%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>96,84%</t>
+          <t>96,56%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -9472,12 +9472,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>141007</t>
+          <t>140487</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>153024</t>
+          <t>153476</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -9487,12 +9487,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>85,48%</t>
+          <t>85,16%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>92,76%</t>
+          <t>93,03%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -9507,12 +9507,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>705566</t>
+          <t>705124</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>787599</t>
+          <t>794012</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -9522,12 +9522,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>85,45%</t>
+          <t>85,4%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>95,39%</t>
+          <t>96,16%</t>
         </is>
       </c>
     </row>
@@ -9667,12 +9667,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>157032</t>
+          <t>161159</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>208535</t>
+          <t>210437</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -9682,12 +9682,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>15,73%</t>
+          <t>16,15%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>20,89%</t>
+          <t>21,08%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -9702,12 +9702,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>41586</t>
+          <t>40768</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>108554</t>
+          <t>109269</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -9717,12 +9717,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>4,34%</t>
+          <t>4,25%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>11,32%</t>
+          <t>11,4%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -9737,12 +9737,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>188524</t>
+          <t>179788</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>304001</t>
+          <t>304944</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -9752,12 +9752,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>9,63%</t>
+          <t>9,19%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>15,53%</t>
+          <t>15,58%</t>
         </is>
       </c>
     </row>
@@ -9780,12 +9780,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>789616</t>
+          <t>787714</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>841119</t>
+          <t>836992</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -9795,12 +9795,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>79,11%</t>
+          <t>78,92%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>84,27%</t>
+          <t>83,85%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -9815,12 +9815,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>850315</t>
+          <t>849600</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>917283</t>
+          <t>918101</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -9830,12 +9830,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>88,68%</t>
+          <t>88,6%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>95,66%</t>
+          <t>95,75%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -9850,12 +9850,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1653019</t>
+          <t>1652076</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1768496</t>
+          <t>1777232</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -9865,12 +9865,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>84,47%</t>
+          <t>84,42%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>90,37%</t>
+          <t>90,81%</t>
         </is>
       </c>
     </row>
@@ -10010,12 +10010,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>99877</t>
+          <t>101485</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>138203</t>
+          <t>138456</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -10025,12 +10025,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>22,76%</t>
+          <t>23,13%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>31,49%</t>
+          <t>31,55%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -10045,12 +10045,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>95520</t>
+          <t>92544</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>154625</t>
+          <t>150808</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -10060,12 +10060,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>11,73%</t>
+          <t>11,37%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>19,0%</t>
+          <t>18,53%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -10080,12 +10080,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>202832</t>
+          <t>207188</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>277260</t>
+          <t>280441</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -10095,12 +10095,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>16,19%</t>
+          <t>16,54%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>22,13%</t>
+          <t>22,38%</t>
         </is>
       </c>
     </row>
@@ -10123,12 +10123,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>300649</t>
+          <t>300396</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>338975</t>
+          <t>337367</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -10138,12 +10138,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>68,51%</t>
+          <t>68,45%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>77,24%</t>
+          <t>76,87%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -10158,12 +10158,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>659356</t>
+          <t>663173</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>718461</t>
+          <t>721437</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -10173,12 +10173,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>81,0%</t>
+          <t>81,47%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>88,27%</t>
+          <t>88,63%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -10193,12 +10193,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>975573</t>
+          <t>972392</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1050001</t>
+          <t>1045645</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -10208,12 +10208,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>77,87%</t>
+          <t>77,62%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>83,81%</t>
+          <t>83,46%</t>
         </is>
       </c>
     </row>
@@ -10353,12 +10353,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>7159</t>
+          <t>6730</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>31698</t>
+          <t>32322</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -10368,12 +10368,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>3,08%</t>
+          <t>2,9%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>13,66%</t>
+          <t>13,92%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -10388,12 +10388,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>84022</t>
+          <t>83174</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>113867</t>
+          <t>112806</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -10403,12 +10403,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>11,29%</t>
+          <t>11,18%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>15,31%</t>
+          <t>15,16%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -10423,12 +10423,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>95874</t>
+          <t>97691</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>135936</t>
+          <t>135262</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -10438,12 +10438,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>9,82%</t>
+          <t>10,01%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>13,93%</t>
+          <t>13,86%</t>
         </is>
       </c>
     </row>
@@ -10466,12 +10466,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>200418</t>
+          <t>199794</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>224957</t>
+          <t>225386</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -10481,12 +10481,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>86,34%</t>
+          <t>86,08%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>96,92%</t>
+          <t>97,1%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -10501,12 +10501,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>630043</t>
+          <t>631104</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>659888</t>
+          <t>660736</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -10516,12 +10516,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>84,69%</t>
+          <t>84,84%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>88,71%</t>
+          <t>88,82%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -10536,12 +10536,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>840090</t>
+          <t>840764</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>880152</t>
+          <t>878335</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -10551,12 +10551,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>86,07%</t>
+          <t>86,14%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>90,18%</t>
+          <t>89,99%</t>
         </is>
       </c>
     </row>
@@ -10696,12 +10696,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>343308</t>
+          <t>374078</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>522622</t>
+          <t>524262</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -10711,12 +10711,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>10,48%</t>
+          <t>11,42%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>15,95%</t>
+          <t>16,0%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -10731,12 +10731,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>298379</t>
+          <t>298303</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>409136</t>
+          <t>408664</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -10751,7 +10751,7 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>11,69%</t>
+          <t>11,68%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -10766,12 +10766,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>726195</t>
+          <t>730355</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>911152</t>
+          <t>915276</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -10781,12 +10781,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>10,72%</t>
+          <t>10,78%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>13,44%</t>
+          <t>13,51%</t>
         </is>
       </c>
     </row>
@@ -10809,12 +10809,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>2754125</t>
+          <t>2752485</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>2933439</t>
+          <t>2902669</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -10824,12 +10824,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>84,05%</t>
+          <t>84,0%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>89,52%</t>
+          <t>88,58%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -10844,12 +10844,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>3091123</t>
+          <t>3091595</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>3201880</t>
+          <t>3201956</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -10859,7 +10859,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>88,31%</t>
+          <t>88,32%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -10879,12 +10879,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>5865854</t>
+          <t>5861730</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>6050811</t>
+          <t>6046651</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -10894,12 +10894,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>86,56%</t>
+          <t>86,49%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>89,28%</t>
+          <t>89,22%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P19C04-Clase-trans_orig.xlsx
+++ b/data/trans_orig/P19C04-Clase-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>36895</t>
+          <t>37555</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>63957</t>
+          <t>63212</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>9,55%</t>
+          <t>9,72%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>16,56%</t>
+          <t>16,36%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>11510</t>
+          <t>11977</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>28902</t>
+          <t>29690</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>4,29%</t>
+          <t>4,46%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>10,77%</t>
+          <t>11,07%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>53851</t>
+          <t>53005</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>86308</t>
+          <t>84615</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>8,23%</t>
+          <t>8,1%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>13,19%</t>
+          <t>12,93%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>322345</t>
+          <t>323090</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>349407</t>
+          <t>348747</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>83,44%</t>
+          <t>83,64%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>90,45%</t>
+          <t>90,28%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>239385</t>
+          <t>238597</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>256777</t>
+          <t>256310</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>89,23%</t>
+          <t>88,93%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>95,71%</t>
+          <t>95,54%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>568282</t>
+          <t>569975</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>600739</t>
+          <t>601585</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>86,81%</t>
+          <t>87,07%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>91,77%</t>
+          <t>91,9%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>35655</t>
+          <t>34525</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>60540</t>
+          <t>60814</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>11,88%</t>
+          <t>11,5%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>20,17%</t>
+          <t>20,26%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>16726</t>
+          <t>16100</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>38387</t>
+          <t>36849</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>5,01%</t>
+          <t>4,83%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>11,51%</t>
+          <t>11,05%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>57365</t>
+          <t>56458</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>91192</t>
+          <t>89237</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>9,05%</t>
+          <t>8,91%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>14,39%</t>
+          <t>14,08%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>239665</t>
+          <t>239391</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>264550</t>
+          <t>265680</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>79,83%</t>
+          <t>79,74%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>88,12%</t>
+          <t>88,5%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>295178</t>
+          <t>296716</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>316839</t>
+          <t>317465</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>88,49%</t>
+          <t>88,95%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>94,99%</t>
+          <t>95,17%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>542578</t>
+          <t>544533</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>576405</t>
+          <t>577312</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>85,61%</t>
+          <t>85,92%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>90,95%</t>
+          <t>91,09%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>76460</t>
+          <t>76311</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>110263</t>
+          <t>110050</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>17,77%</t>
+          <t>17,74%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>25,63%</t>
+          <t>25,58%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>12180</t>
+          <t>12278</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>27691</t>
+          <t>28169</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>8,7%</t>
+          <t>8,77%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>19,77%</t>
+          <t>20,11%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>92742</t>
+          <t>92135</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>131694</t>
+          <t>129375</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>16,26%</t>
+          <t>16,15%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>23,09%</t>
+          <t>22,68%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>320004</t>
+          <t>320217</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>353807</t>
+          <t>353956</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>74,37%</t>
+          <t>74,42%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>82,23%</t>
+          <t>82,26%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>112377</t>
+          <t>111899</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>127888</t>
+          <t>127790</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>80,23%</t>
+          <t>79,89%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>91,3%</t>
+          <t>91,23%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>438641</t>
+          <t>440960</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>477593</t>
+          <t>478200</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>76,91%</t>
+          <t>77,32%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>83,74%</t>
+          <t>83,85%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>194310</t>
+          <t>195334</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>246408</t>
+          <t>248207</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>22,3%</t>
+          <t>22,41%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>28,28%</t>
+          <t>28,48%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>79251</t>
+          <t>78309</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>115002</t>
+          <t>114499</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>13,29%</t>
+          <t>13,13%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>19,29%</t>
+          <t>19,2%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>286361</t>
+          <t>286485</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>348190</t>
+          <t>347979</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>19,51%</t>
+          <t>19,52%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>23,72%</t>
+          <t>23,71%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>625046</t>
+          <t>623247</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>677144</t>
+          <t>676120</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>71,72%</t>
+          <t>71,52%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>77,7%</t>
+          <t>77,59%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>481247</t>
+          <t>481750</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>516998</t>
+          <t>517940</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>80,71%</t>
+          <t>80,8%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>86,71%</t>
+          <t>86,87%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1119512</t>
+          <t>1119723</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1181341</t>
+          <t>1181217</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>76,28%</t>
+          <t>76,29%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>80,49%</t>
+          <t>80,48%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>47647</t>
+          <t>46797</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>76333</t>
+          <t>73115</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>19,22%</t>
+          <t>18,88%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>30,79%</t>
+          <t>29,49%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>74254</t>
+          <t>76055</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>110131</t>
+          <t>108859</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>16,28%</t>
+          <t>16,68%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>24,15%</t>
+          <t>23,87%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>130768</t>
+          <t>130394</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>174200</t>
+          <t>173593</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>18,57%</t>
+          <t>18,52%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>24,74%</t>
+          <t>24,66%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>171594</t>
+          <t>174812</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>200280</t>
+          <t>201130</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>69,21%</t>
+          <t>70,51%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>80,78%</t>
+          <t>81,12%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>345949</t>
+          <t>347221</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>381826</t>
+          <t>380025</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>75,85%</t>
+          <t>76,13%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>83,72%</t>
+          <t>83,32%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>529807</t>
+          <t>530414</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>573239</t>
+          <t>573613</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>75,26%</t>
+          <t>75,34%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>81,43%</t>
+          <t>81,48%</t>
         </is>
       </c>
     </row>
@@ -2428,7 +2428,7 @@
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -2448,12 +2448,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>12554</t>
+          <t>13139</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>30376</t>
+          <t>31712</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2463,12 +2463,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>5,91%</t>
+          <t>6,19%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>14,31%</t>
+          <t>14,94%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2483,12 +2483,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>133400</t>
+          <t>131779</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>176658</t>
+          <t>174498</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2498,12 +2498,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>14,11%</t>
+          <t>13,94%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>18,68%</t>
+          <t>18,45%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2518,12 +2518,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>152195</t>
+          <t>149376</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>199572</t>
+          <t>196009</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2533,12 +2533,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>13,14%</t>
+          <t>12,9%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>17,24%</t>
+          <t>16,93%</t>
         </is>
       </c>
     </row>
@@ -2561,12 +2561,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>181857</t>
+          <t>180521</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>199679</t>
+          <t>199094</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2576,12 +2576,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>85,69%</t>
+          <t>85,06%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>94,09%</t>
+          <t>93,81%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2596,12 +2596,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>768958</t>
+          <t>771118</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>812216</t>
+          <t>813837</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2611,12 +2611,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>81,32%</t>
+          <t>81,55%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>85,89%</t>
+          <t>86,06%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2631,12 +2631,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>958277</t>
+          <t>961840</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>1005654</t>
+          <t>1008473</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2646,12 +2646,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>82,76%</t>
+          <t>83,07%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>86,86%</t>
+          <t>87,1%</t>
         </is>
       </c>
     </row>
@@ -2791,12 +2791,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>449655</t>
+          <t>450707</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>530314</t>
+          <t>531133</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2806,12 +2806,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>18,37%</t>
+          <t>18,41%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>21,66%</t>
+          <t>21,69%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>363243</t>
+          <t>369894</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>436091</t>
+          <t>444588</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2841,12 +2841,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>13,26%</t>
+          <t>13,5%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>15,92%</t>
+          <t>16,23%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>838981</t>
+          <t>839142</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>952127</t>
+          <t>948703</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2881,7 +2881,7 @@
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>18,35%</t>
+          <t>18,29%</t>
         </is>
       </c>
     </row>
@@ -2904,12 +2904,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>1918074</t>
+          <t>1917255</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>1998733</t>
+          <t>1997681</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>78,34%</t>
+          <t>78,31%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>81,63%</t>
+          <t>81,59%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2939,12 +2939,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>2303773</t>
+          <t>2295276</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>2376621</t>
+          <t>2369970</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2954,12 +2954,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>84,08%</t>
+          <t>83,77%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>86,74%</t>
+          <t>86,5%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2974,12 +2974,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>4236125</t>
+          <t>4239549</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>4349271</t>
+          <t>4349110</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2989,7 +2989,7 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>81,65%</t>
+          <t>81,71%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
@@ -3368,12 +3368,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>40740</t>
+          <t>39487</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>71399</t>
+          <t>69971</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3383,12 +3383,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>10,3%</t>
+          <t>9,99%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>18,06%</t>
+          <t>17,7%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3403,12 +3403,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>21410</t>
+          <t>21229</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>44333</t>
+          <t>45131</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3418,12 +3418,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>7,28%</t>
+          <t>7,22%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>15,08%</t>
+          <t>15,35%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3438,12 +3438,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>67515</t>
+          <t>66867</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>104549</t>
+          <t>103553</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3453,12 +3453,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>9,79%</t>
+          <t>9,7%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>15,17%</t>
+          <t>15,02%</t>
         </is>
       </c>
     </row>
@@ -3481,12 +3481,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>323945</t>
+          <t>325373</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>354604</t>
+          <t>355857</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3496,12 +3496,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>81,94%</t>
+          <t>82,3%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>89,7%</t>
+          <t>90,01%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3516,12 +3516,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>249621</t>
+          <t>248823</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>272544</t>
+          <t>272725</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3531,12 +3531,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>84,92%</t>
+          <t>84,65%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>92,72%</t>
+          <t>92,78%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3551,12 +3551,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>584750</t>
+          <t>585746</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>621784</t>
+          <t>622432</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3566,12 +3566,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>84,83%</t>
+          <t>84,98%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>90,21%</t>
+          <t>90,3%</t>
         </is>
       </c>
     </row>
@@ -3711,12 +3711,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>43593</t>
+          <t>42271</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>74484</t>
+          <t>71126</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3726,12 +3726,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>11,36%</t>
+          <t>11,02%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>19,41%</t>
+          <t>18,54%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3746,12 +3746,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>23245</t>
+          <t>24237</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>45811</t>
+          <t>47866</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3761,12 +3761,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>7,41%</t>
+          <t>7,73%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>14,61%</t>
+          <t>15,27%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3781,12 +3781,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>72322</t>
+          <t>71967</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>110812</t>
+          <t>108175</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3796,12 +3796,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>10,37%</t>
+          <t>10,32%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>15,89%</t>
+          <t>15,52%</t>
         </is>
       </c>
     </row>
@@ -3824,12 +3824,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>309240</t>
+          <t>312598</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>340131</t>
+          <t>341453</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3839,12 +3839,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>80,59%</t>
+          <t>81,46%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>88,64%</t>
+          <t>88,98%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3859,12 +3859,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>267690</t>
+          <t>265635</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>290256</t>
+          <t>289264</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3874,12 +3874,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>85,39%</t>
+          <t>84,73%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>92,59%</t>
+          <t>92,27%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3894,12 +3894,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>586413</t>
+          <t>589050</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>624903</t>
+          <t>625258</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3909,12 +3909,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>84,11%</t>
+          <t>84,48%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>89,63%</t>
+          <t>89,68%</t>
         </is>
       </c>
     </row>
@@ -4054,12 +4054,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>121322</t>
+          <t>120924</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>162313</t>
+          <t>162110</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4069,12 +4069,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>22,66%</t>
+          <t>22,58%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>30,31%</t>
+          <t>30,27%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4089,12 +4089,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>18126</t>
+          <t>17802</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>38586</t>
+          <t>38066</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4104,12 +4104,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>7,56%</t>
+          <t>7,43%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>16,1%</t>
+          <t>15,88%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4124,12 +4124,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>143651</t>
+          <t>145131</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>190546</t>
+          <t>192882</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4139,12 +4139,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>18,53%</t>
+          <t>18,72%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>24,58%</t>
+          <t>24,88%</t>
         </is>
       </c>
     </row>
@@ -4167,12 +4167,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>373175</t>
+          <t>373378</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>414166</t>
+          <t>414564</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4182,12 +4182,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>69,69%</t>
+          <t>69,73%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>77,34%</t>
+          <t>77,42%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4202,12 +4202,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>201052</t>
+          <t>201572</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>221512</t>
+          <t>221836</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4217,12 +4217,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>83,9%</t>
+          <t>84,12%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>92,44%</t>
+          <t>92,57%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4237,12 +4237,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>584579</t>
+          <t>582243</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>631474</t>
+          <t>629994</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4252,12 +4252,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>75,42%</t>
+          <t>75,12%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>81,47%</t>
+          <t>81,28%</t>
         </is>
       </c>
     </row>
@@ -4397,12 +4397,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>284292</t>
+          <t>286155</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>346455</t>
+          <t>346495</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4412,7 +4412,7 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>29,23%</t>
+          <t>29,42%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
@@ -4432,12 +4432,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>88548</t>
+          <t>89307</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>128259</t>
+          <t>128677</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4447,12 +4447,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>12,67%</t>
+          <t>12,78%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>18,35%</t>
+          <t>18,41%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4467,12 +4467,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>385587</t>
+          <t>387257</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>460639</t>
+          <t>458643</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4482,12 +4482,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>23,07%</t>
+          <t>23,17%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>27,56%</t>
+          <t>27,44%</t>
         </is>
       </c>
     </row>
@@ -4510,12 +4510,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>626274</t>
+          <t>626234</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>688437</t>
+          <t>686574</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4530,7 +4530,7 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>70,77%</t>
+          <t>70,58%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4545,12 +4545,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>570668</t>
+          <t>570250</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>610379</t>
+          <t>609620</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4560,12 +4560,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>81,65%</t>
+          <t>81,59%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>87,33%</t>
+          <t>87,22%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4580,12 +4580,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1211017</t>
+          <t>1213013</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1286069</t>
+          <t>1284399</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4595,12 +4595,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>72,44%</t>
+          <t>72,56%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>76,93%</t>
+          <t>76,83%</t>
         </is>
       </c>
     </row>
@@ -4740,12 +4740,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>117077</t>
+          <t>116688</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>155872</t>
+          <t>154374</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4755,12 +4755,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>29,03%</t>
+          <t>28,93%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>38,65%</t>
+          <t>38,28%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4775,12 +4775,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>140111</t>
+          <t>138458</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>184568</t>
+          <t>182721</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4790,12 +4790,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>20,95%</t>
+          <t>20,7%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>27,6%</t>
+          <t>27,32%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4810,12 +4810,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>269972</t>
+          <t>266371</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>326092</t>
+          <t>326014</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4825,12 +4825,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>25,18%</t>
+          <t>24,85%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>30,42%</t>
+          <t>30,41%</t>
         </is>
       </c>
     </row>
@@ -4853,12 +4853,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>247440</t>
+          <t>248938</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>286235</t>
+          <t>286624</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4868,12 +4868,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>61,35%</t>
+          <t>61,72%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>70,97%</t>
+          <t>71,07%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4888,12 +4888,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>484191</t>
+          <t>486038</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>528648</t>
+          <t>530301</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4903,12 +4903,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>72,4%</t>
+          <t>72,68%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>79,05%</t>
+          <t>79,3%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4923,12 +4923,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>745979</t>
+          <t>746057</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>802099</t>
+          <t>805700</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4938,12 +4938,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>69,58%</t>
+          <t>69,59%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>74,82%</t>
+          <t>75,15%</t>
         </is>
       </c>
     </row>
@@ -5063,7 +5063,7 @@
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -5083,12 +5083,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>13505</t>
+          <t>14026</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>30489</t>
+          <t>30691</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5098,12 +5098,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>6,11%</t>
+          <t>6,34%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>13,78%</t>
+          <t>13,87%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5118,12 +5118,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>168929</t>
+          <t>168877</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>217917</t>
+          <t>217128</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5133,12 +5133,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>18,24%</t>
+          <t>18,23%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>23,52%</t>
+          <t>23,44%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5153,12 +5153,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>190138</t>
+          <t>188467</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>239873</t>
+          <t>238837</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5168,12 +5168,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>16,57%</t>
+          <t>16,42%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>20,9%</t>
+          <t>20,81%</t>
         </is>
       </c>
     </row>
@@ -5196,12 +5196,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>190714</t>
+          <t>190512</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>207698</t>
+          <t>207177</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5211,12 +5211,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>86,22%</t>
+          <t>86,13%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>93,89%</t>
+          <t>93,66%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5231,12 +5231,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>708460</t>
+          <t>709249</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>757448</t>
+          <t>757500</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5246,12 +5246,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>76,48%</t>
+          <t>76,56%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>81,76%</t>
+          <t>81,77%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5266,12 +5266,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>907707</t>
+          <t>908743</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>957442</t>
+          <t>959113</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5281,12 +5281,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>79,1%</t>
+          <t>79,19%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>83,43%</t>
+          <t>83,58%</t>
         </is>
       </c>
     </row>
@@ -5426,12 +5426,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>671919</t>
+          <t>673751</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>771843</t>
+          <t>770563</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5441,12 +5441,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>23,08%</t>
+          <t>23,14%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>26,51%</t>
+          <t>26,46%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5461,12 +5461,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>509463</t>
+          <t>512519</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>594915</t>
+          <t>594991</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5476,7 +5476,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>16,22%</t>
+          <t>16,32%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -5496,12 +5496,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>1210570</t>
+          <t>1208281</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>1337341</t>
+          <t>1336361</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5511,12 +5511,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>20,0%</t>
+          <t>19,96%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>22,09%</t>
+          <t>22,08%</t>
         </is>
       </c>
     </row>
@@ -5539,12 +5539,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>2139957</t>
+          <t>2141237</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>2239881</t>
+          <t>2238049</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -5554,12 +5554,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>73,49%</t>
+          <t>73,54%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>76,92%</t>
+          <t>76,86%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -5574,12 +5574,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>2546241</t>
+          <t>2546165</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>2631693</t>
+          <t>2628637</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -5594,7 +5594,7 @@
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>83,78%</t>
+          <t>83,68%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -5609,12 +5609,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>4715615</t>
+          <t>4716595</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>4842386</t>
+          <t>4844675</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -5624,12 +5624,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>77,91%</t>
+          <t>77,92%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>80,0%</t>
+          <t>80,04%</t>
         </is>
       </c>
     </row>
@@ -6003,12 +6003,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>24580</t>
+          <t>24110</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>47609</t>
+          <t>47616</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6018,7 +6018,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>6,34%</t>
+          <t>6,22%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -6038,12 +6038,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>16306</t>
+          <t>15468</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>34792</t>
+          <t>34836</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6053,12 +6053,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>5,16%</t>
+          <t>4,9%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>11,02%</t>
+          <t>11,03%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6073,12 +6073,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>43896</t>
+          <t>45637</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>74755</t>
+          <t>76438</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6088,12 +6088,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>6,24%</t>
+          <t>6,49%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>10,63%</t>
+          <t>10,87%</t>
         </is>
       </c>
     </row>
@@ -6116,12 +6116,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>340005</t>
+          <t>339998</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>363034</t>
+          <t>363504</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -6136,7 +6136,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>93,66%</t>
+          <t>93,78%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6151,12 +6151,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>281024</t>
+          <t>280980</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>299510</t>
+          <t>300348</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -6166,12 +6166,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>88,98%</t>
+          <t>88,97%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>94,84%</t>
+          <t>95,1%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6186,12 +6186,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>628675</t>
+          <t>626992</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>659534</t>
+          <t>657793</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -6201,12 +6201,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>89,37%</t>
+          <t>89,13%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>93,76%</t>
+          <t>93,51%</t>
         </is>
       </c>
     </row>
@@ -6346,12 +6346,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>28942</t>
+          <t>28482</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>54499</t>
+          <t>54042</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -6361,12 +6361,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>9,14%</t>
+          <t>8,99%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>17,21%</t>
+          <t>17,07%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -6381,12 +6381,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>11523</t>
+          <t>11801</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>29846</t>
+          <t>31295</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -6396,12 +6396,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>3,45%</t>
+          <t>3,54%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>8,95%</t>
+          <t>9,38%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6416,12 +6416,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>45438</t>
+          <t>45984</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>77299</t>
+          <t>77188</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -6431,12 +6431,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>6,99%</t>
+          <t>7,07%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>11,89%</t>
+          <t>11,87%</t>
         </is>
       </c>
     </row>
@@ -6459,12 +6459,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>262159</t>
+          <t>262616</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>287716</t>
+          <t>288176</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -6474,12 +6474,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>82,79%</t>
+          <t>82,93%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>90,86%</t>
+          <t>91,01%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -6494,12 +6494,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>303729</t>
+          <t>302280</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>322052</t>
+          <t>321774</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -6509,12 +6509,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>91,05%</t>
+          <t>90,62%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>96,55%</t>
+          <t>96,46%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -6529,12 +6529,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>572933</t>
+          <t>573044</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>604794</t>
+          <t>604248</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -6544,12 +6544,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>88,11%</t>
+          <t>88,13%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>93,01%</t>
+          <t>92,93%</t>
         </is>
       </c>
     </row>
@@ -6689,12 +6689,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>58895</t>
+          <t>58667</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>89887</t>
+          <t>88960</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -6704,12 +6704,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>14,53%</t>
+          <t>14,48%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>22,18%</t>
+          <t>21,95%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6724,12 +6724,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>13876</t>
+          <t>13535</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>32739</t>
+          <t>33408</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -6739,12 +6739,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>9,95%</t>
+          <t>9,71%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>23,48%</t>
+          <t>23,96%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6759,12 +6759,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>78647</t>
+          <t>78194</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>114083</t>
+          <t>115377</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -6774,12 +6774,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>14,44%</t>
+          <t>14,36%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>20,95%</t>
+          <t>21,18%</t>
         </is>
       </c>
     </row>
@@ -6802,12 +6802,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>315324</t>
+          <t>316251</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>346316</t>
+          <t>346544</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -6817,12 +6817,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>77,82%</t>
+          <t>78,05%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>85,47%</t>
+          <t>85,52%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -6837,12 +6837,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>106682</t>
+          <t>106013</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>125545</t>
+          <t>125886</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -6852,12 +6852,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>76,52%</t>
+          <t>76,04%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>90,05%</t>
+          <t>90,29%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -6872,12 +6872,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>430550</t>
+          <t>429256</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>465986</t>
+          <t>466439</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -6887,12 +6887,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>79,05%</t>
+          <t>78,82%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>85,56%</t>
+          <t>85,64%</t>
         </is>
       </c>
     </row>
@@ -7032,12 +7032,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>163704</t>
+          <t>164103</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>212217</t>
+          <t>210838</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7047,12 +7047,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>18,61%</t>
+          <t>18,66%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>24,13%</t>
+          <t>23,97%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7067,12 +7067,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>68099</t>
+          <t>68909</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>103746</t>
+          <t>103944</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7082,12 +7082,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>9,97%</t>
+          <t>10,09%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>15,19%</t>
+          <t>15,22%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7102,12 +7102,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>242213</t>
+          <t>242201</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>305247</t>
+          <t>302684</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7122,7 +7122,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>19,54%</t>
+          <t>19,37%</t>
         </is>
       </c>
     </row>
@@ -7145,12 +7145,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>667288</t>
+          <t>668667</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>715801</t>
+          <t>715402</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7160,12 +7160,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>75,87%</t>
+          <t>76,03%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>81,39%</t>
+          <t>81,34%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7180,12 +7180,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>579190</t>
+          <t>578992</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>614837</t>
+          <t>614027</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7195,12 +7195,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>84,81%</t>
+          <t>84,78%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>90,03%</t>
+          <t>89,91%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7215,12 +7215,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1257194</t>
+          <t>1259757</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1320228</t>
+          <t>1320240</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7230,7 +7230,7 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>80,46%</t>
+          <t>80,63%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -7375,12 +7375,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>99276</t>
+          <t>99169</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>138041</t>
+          <t>135610</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -7390,12 +7390,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>23,35%</t>
+          <t>23,32%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>32,47%</t>
+          <t>31,9%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7410,12 +7410,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>70026</t>
+          <t>69803</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>106544</t>
+          <t>103771</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -7425,12 +7425,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>12,56%</t>
+          <t>12,52%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>19,11%</t>
+          <t>18,61%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -7445,12 +7445,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>179105</t>
+          <t>179137</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>231259</t>
+          <t>229234</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -7465,7 +7465,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>23,53%</t>
+          <t>23,33%</t>
         </is>
       </c>
     </row>
@@ -7488,12 +7488,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>287128</t>
+          <t>289559</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>325893</t>
+          <t>326000</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -7503,12 +7503,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>67,53%</t>
+          <t>68,1%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>76,65%</t>
+          <t>76,68%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -7523,12 +7523,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>450937</t>
+          <t>453710</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>487455</t>
+          <t>487678</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -7538,12 +7538,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>80,89%</t>
+          <t>81,39%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>87,44%</t>
+          <t>87,48%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -7558,12 +7558,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>751391</t>
+          <t>753416</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>803545</t>
+          <t>803513</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -7573,7 +7573,7 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>76,47%</t>
+          <t>76,67%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
@@ -7698,7 +7698,7 @@
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -7718,12 +7718,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>15078</t>
+          <t>14430</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>32664</t>
+          <t>32883</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -7733,12 +7733,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>6,24%</t>
+          <t>5,97%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>13,52%</t>
+          <t>13,61%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -7753,12 +7753,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>115360</t>
+          <t>112562</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>160839</t>
+          <t>158031</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -7768,12 +7768,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>13,98%</t>
+          <t>13,64%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>19,49%</t>
+          <t>19,15%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -7788,12 +7788,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>134473</t>
+          <t>135890</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>182716</t>
+          <t>183967</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -7803,12 +7803,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>12,6%</t>
+          <t>12,74%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>17,13%</t>
+          <t>17,24%</t>
         </is>
       </c>
     </row>
@@ -7831,12 +7831,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>208884</t>
+          <t>208665</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>226470</t>
+          <t>227118</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -7846,12 +7846,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>86,48%</t>
+          <t>86,39%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>93,76%</t>
+          <t>94,03%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -7866,12 +7866,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>664450</t>
+          <t>667258</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>709929</t>
+          <t>712727</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -7881,12 +7881,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>80,51%</t>
+          <t>80,85%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>86,02%</t>
+          <t>86,36%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -7901,12 +7901,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>884121</t>
+          <t>882870</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>932364</t>
+          <t>930947</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -7916,12 +7916,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>82,87%</t>
+          <t>82,76%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>87,4%</t>
+          <t>87,26%</t>
         </is>
       </c>
     </row>
@@ -8061,12 +8061,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>436941</t>
+          <t>437729</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>515877</t>
+          <t>518628</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -8076,12 +8076,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>16,45%</t>
+          <t>16,48%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>19,43%</t>
+          <t>19,53%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -8096,12 +8096,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>337750</t>
+          <t>337152</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>413760</t>
+          <t>418827</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -8111,12 +8111,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>11,83%</t>
+          <t>11,81%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>14,49%</t>
+          <t>14,67%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -8131,12 +8131,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>795535</t>
+          <t>791357</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>906355</t>
+          <t>903800</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -8146,12 +8146,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>14,44%</t>
+          <t>14,36%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>16,45%</t>
+          <t>16,4%</t>
         </is>
       </c>
     </row>
@@ -8174,12 +8174,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>2139828</t>
+          <t>2137077</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>2218764</t>
+          <t>2217976</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -8189,12 +8189,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>80,57%</t>
+          <t>80,47%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>83,55%</t>
+          <t>83,52%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -8209,12 +8209,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>2440758</t>
+          <t>2435691</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>2516768</t>
+          <t>2517366</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -8224,12 +8224,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>85,51%</t>
+          <t>85,33%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>88,17%</t>
+          <t>88,19%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -8244,12 +8244,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>4603868</t>
+          <t>4606423</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>4714688</t>
+          <t>4718866</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -8259,12 +8259,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>83,55%</t>
+          <t>83,6%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>85,56%</t>
+          <t>85,64%</t>
         </is>
       </c>
     </row>
@@ -8633,27 +8633,27 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>41913</t>
+          <t>45624</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>30329</t>
+          <t>33697</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>54686</t>
+          <t>59393</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>8,41%</t>
+          <t>8,43%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>6,08%</t>
+          <t>6,23%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -8668,32 +8668,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>20881</t>
+          <t>22440</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>14373</t>
+          <t>15757</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>28515</t>
+          <t>30817</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>4,74%</t>
+          <t>4,66%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>3,26%</t>
+          <t>3,27%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>6,47%</t>
+          <t>6,4%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -8703,32 +8703,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>62794</t>
+          <t>68064</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>51039</t>
+          <t>53987</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>77793</t>
+          <t>84592</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>6,68%</t>
+          <t>6,66%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>5,43%</t>
+          <t>5,28%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>8,28%</t>
+          <t>8,27%</t>
         </is>
       </c>
     </row>
@@ -8746,22 +8746,22 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>456569</t>
+          <t>495639</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>443796</t>
+          <t>481870</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>468153</t>
+          <t>507566</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>91,59%</t>
+          <t>91,57%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
@@ -8771,7 +8771,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>93,92%</t>
+          <t>93,77%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -8781,32 +8781,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>420044</t>
+          <t>458887</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>412410</t>
+          <t>450510</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>426552</t>
+          <t>465570</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>95,26%</t>
+          <t>95,34%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>93,53%</t>
+          <t>93,6%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>96,74%</t>
+          <t>96,73%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -8816,32 +8816,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>876613</t>
+          <t>954526</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>861614</t>
+          <t>937998</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>888368</t>
+          <t>968603</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>93,32%</t>
+          <t>93,34%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>91,72%</t>
+          <t>91,73%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>94,57%</t>
+          <t>94,72%</t>
         </is>
       </c>
     </row>
@@ -8859,17 +8859,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>498482</t>
+          <t>541263</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>498482</t>
+          <t>541263</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>498482</t>
+          <t>541263</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -8894,17 +8894,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>440925</t>
+          <t>481327</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>440925</t>
+          <t>481327</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>440925</t>
+          <t>481327</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -8929,17 +8929,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>939407</t>
+          <t>1022590</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>939407</t>
+          <t>1022590</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>939407</t>
+          <t>1022590</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -8976,27 +8976,27 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>45814</t>
+          <t>48458</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>33948</t>
+          <t>36401</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>60009</t>
+          <t>64142</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>10,22%</t>
+          <t>10,11%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>7,57%</t>
+          <t>7,59%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
@@ -9011,32 +9011,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>21822</t>
+          <t>24470</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>15089</t>
+          <t>17609</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>30977</t>
+          <t>34940</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>5,78%</t>
+          <t>5,86%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>4,0%</t>
+          <t>4,21%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>8,2%</t>
+          <t>8,36%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -9046,32 +9046,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>67636</t>
+          <t>72928</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>54321</t>
+          <t>58694</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>84113</t>
+          <t>89449</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>8,19%</t>
+          <t>8,13%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>6,58%</t>
+          <t>6,54%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>10,18%</t>
+          <t>9,97%</t>
         </is>
       </c>
     </row>
@@ -9089,22 +9089,22 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>402604</t>
+          <t>430874</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>388409</t>
+          <t>415190</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>414470</t>
+          <t>442931</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>89,78%</t>
+          <t>89,89%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
@@ -9114,7 +9114,7 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>92,43%</t>
+          <t>92,41%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -9124,32 +9124,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>355784</t>
+          <t>393450</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>346629</t>
+          <t>382980</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>362517</t>
+          <t>400311</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>94,22%</t>
+          <t>94,14%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>91,8%</t>
+          <t>91,64%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>96,0%</t>
+          <t>95,79%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -9159,32 +9159,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>758387</t>
+          <t>824325</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>741910</t>
+          <t>807804</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>771702</t>
+          <t>838559</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>91,81%</t>
+          <t>91,87%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>89,82%</t>
+          <t>90,03%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>93,42%</t>
+          <t>93,46%</t>
         </is>
       </c>
     </row>
@@ -9202,17 +9202,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>448418</t>
+          <t>479332</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>448418</t>
+          <t>479332</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>448418</t>
+          <t>479332</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -9237,17 +9237,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>377606</t>
+          <t>417920</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>377606</t>
+          <t>417920</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>377606</t>
+          <t>417920</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -9272,17 +9272,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>826023</t>
+          <t>897253</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>826023</t>
+          <t>897253</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>826023</t>
+          <t>897253</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -9319,32 +9319,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>62681</t>
+          <t>72973</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>22701</t>
+          <t>57094</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>106188</t>
+          <t>89562</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>9,49%</t>
+          <t>15,73%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>3,44%</t>
+          <t>12,31%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>16,07%</t>
+          <t>19,31%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -9354,32 +9354,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>17211</t>
+          <t>19248</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>11492</t>
+          <t>13508</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>24481</t>
+          <t>26807</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>10,43%</t>
+          <t>10,41%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>6,97%</t>
+          <t>7,31%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>14,84%</t>
+          <t>14,5%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -9389,32 +9389,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>79892</t>
+          <t>92220</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>31685</t>
+          <t>76190</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>120573</t>
+          <t>110189</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>9,68%</t>
+          <t>14,22%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>3,84%</t>
+          <t>11,75%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>14,6%</t>
+          <t>16,99%</t>
         </is>
       </c>
     </row>
@@ -9432,32 +9432,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>598048</t>
+          <t>390892</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>554541</t>
+          <t>374303</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>638028</t>
+          <t>406771</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>90,51%</t>
+          <t>84,27%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>83,93%</t>
+          <t>80,69%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>96,56%</t>
+          <t>87,69%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -9467,32 +9467,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>147757</t>
+          <t>165585</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>140487</t>
+          <t>158026</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>153476</t>
+          <t>171325</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>89,57%</t>
+          <t>89,59%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>85,16%</t>
+          <t>85,5%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>93,03%</t>
+          <t>92,69%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -9502,32 +9502,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>745805</t>
+          <t>556478</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>705124</t>
+          <t>538509</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>794012</t>
+          <t>572508</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>90,32%</t>
+          <t>85,78%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>85,4%</t>
+          <t>83,01%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>96,16%</t>
+          <t>88,25%</t>
         </is>
       </c>
     </row>
@@ -9545,17 +9545,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>660729</t>
+          <t>463865</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>660729</t>
+          <t>463865</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>660729</t>
+          <t>463865</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -9580,17 +9580,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>164968</t>
+          <t>184833</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>164968</t>
+          <t>184833</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>164968</t>
+          <t>184833</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -9615,17 +9615,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>825697</t>
+          <t>648698</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>825697</t>
+          <t>648698</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>825697</t>
+          <t>648698</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -9662,32 +9662,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>182376</t>
+          <t>207364</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>161159</t>
+          <t>183274</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>210437</t>
+          <t>235408</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>18,27%</t>
+          <t>18,93%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>16,15%</t>
+          <t>16,73%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>21,08%</t>
+          <t>21,48%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -9697,32 +9697,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>80423</t>
+          <t>91117</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>40768</t>
+          <t>77111</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>109269</t>
+          <t>106793</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>8,39%</t>
+          <t>10,89%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>4,25%</t>
+          <t>9,22%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>11,4%</t>
+          <t>12,76%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -9732,32 +9732,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>262799</t>
+          <t>298481</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>179788</t>
+          <t>269054</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>304944</t>
+          <t>331239</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>13,43%</t>
+          <t>15,45%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>9,19%</t>
+          <t>13,92%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>15,58%</t>
+          <t>17,14%</t>
         </is>
       </c>
     </row>
@@ -9775,32 +9775,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>815775</t>
+          <t>888335</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>787714</t>
+          <t>860291</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>836992</t>
+          <t>912425</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>81,73%</t>
+          <t>81,07%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>78,92%</t>
+          <t>78,52%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>83,85%</t>
+          <t>83,27%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -9810,32 +9810,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>878446</t>
+          <t>745673</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>849600</t>
+          <t>729997</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>918101</t>
+          <t>759679</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>91,61%</t>
+          <t>89,11%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>88,6%</t>
+          <t>87,24%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>95,75%</t>
+          <t>90,78%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -9845,32 +9845,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>1694221</t>
+          <t>1634008</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1652076</t>
+          <t>1601250</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1777232</t>
+          <t>1663435</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>86,57%</t>
+          <t>84,55%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>84,42%</t>
+          <t>82,86%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>90,81%</t>
+          <t>86,08%</t>
         </is>
       </c>
     </row>
@@ -9888,17 +9888,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>998151</t>
+          <t>1095699</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>998151</t>
+          <t>1095699</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>998151</t>
+          <t>1095699</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -9923,17 +9923,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>958869</t>
+          <t>836790</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>958869</t>
+          <t>836790</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>958869</t>
+          <t>836790</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -9958,17 +9958,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>1957020</t>
+          <t>1932489</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>1957020</t>
+          <t>1932489</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>1957020</t>
+          <t>1932489</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -10005,32 +10005,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>118644</t>
+          <t>147869</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>101485</t>
+          <t>128880</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>138456</t>
+          <t>171045</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>27,04%</t>
+          <t>29,0%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>23,13%</t>
+          <t>25,28%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>31,55%</t>
+          <t>33,55%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -10040,32 +10040,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>129762</t>
+          <t>141802</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>92544</t>
+          <t>125094</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>150808</t>
+          <t>157682</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>15,94%</t>
+          <t>17,87%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>11,37%</t>
+          <t>15,76%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>18,53%</t>
+          <t>19,87%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -10075,32 +10075,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>248406</t>
+          <t>289670</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>207188</t>
+          <t>265473</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>280441</t>
+          <t>320530</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>19,83%</t>
+          <t>22,23%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>16,54%</t>
+          <t>20,37%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>22,38%</t>
+          <t>24,59%</t>
         </is>
       </c>
     </row>
@@ -10118,32 +10118,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>320208</t>
+          <t>361979</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>300396</t>
+          <t>338803</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>337367</t>
+          <t>380968</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>72,96%</t>
+          <t>71,0%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>68,45%</t>
+          <t>66,45%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>76,87%</t>
+          <t>74,72%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -10153,32 +10153,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>684219</t>
+          <t>651703</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>663173</t>
+          <t>635823</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>721437</t>
+          <t>668411</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>84,06%</t>
+          <t>82,13%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>81,47%</t>
+          <t>80,13%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>88,63%</t>
+          <t>84,24%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -10188,32 +10188,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>1004427</t>
+          <t>1013683</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>972392</t>
+          <t>982823</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1045645</t>
+          <t>1037880</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>80,17%</t>
+          <t>77,77%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>77,62%</t>
+          <t>75,41%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>83,46%</t>
+          <t>79,63%</t>
         </is>
       </c>
     </row>
@@ -10231,17 +10231,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>438852</t>
+          <t>509848</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>438852</t>
+          <t>509848</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>438852</t>
+          <t>509848</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -10266,17 +10266,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>813981</t>
+          <t>793505</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>813981</t>
+          <t>793505</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>813981</t>
+          <t>793505</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -10301,17 +10301,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>1252833</t>
+          <t>1303353</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1252833</t>
+          <t>1303353</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>1252833</t>
+          <t>1303353</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -10333,7 +10333,7 @@
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -10348,102 +10348,102 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>16136</t>
+          <t>16064</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>6730</t>
+          <t>7690</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>32322</t>
+          <t>32115</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>6,95%</t>
+          <t>7,15%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>2,9%</t>
+          <t>3,42%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
+          <t>14,3%</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
+          <t>176</t>
+        </is>
+      </c>
+      <c r="K19" s="2" t="inlineStr">
+        <is>
+          <t>106900</t>
+        </is>
+      </c>
+      <c r="L19" s="2" t="inlineStr">
+        <is>
+          <t>91863</t>
+        </is>
+      </c>
+      <c r="M19" s="2" t="inlineStr">
+        <is>
+          <t>124788</t>
+        </is>
+      </c>
+      <c r="N19" s="2" t="inlineStr">
+        <is>
+          <t>13,06%</t>
+        </is>
+      </c>
+      <c r="O19" s="2" t="inlineStr">
+        <is>
+          <t>11,22%</t>
+        </is>
+      </c>
+      <c r="P19" s="2" t="inlineStr">
+        <is>
+          <t>15,24%</t>
+        </is>
+      </c>
+      <c r="Q19" s="2" t="inlineStr">
+        <is>
+          <t>186</t>
+        </is>
+      </c>
+      <c r="R19" s="2" t="inlineStr">
+        <is>
+          <t>122964</t>
+        </is>
+      </c>
+      <c r="S19" s="2" t="inlineStr">
+        <is>
+          <t>103924</t>
+        </is>
+      </c>
+      <c r="T19" s="2" t="inlineStr">
+        <is>
+          <t>145216</t>
+        </is>
+      </c>
+      <c r="U19" s="2" t="inlineStr">
+        <is>
+          <t>11,79%</t>
+        </is>
+      </c>
+      <c r="V19" s="2" t="inlineStr">
+        <is>
+          <t>9,96%</t>
+        </is>
+      </c>
+      <c r="W19" s="2" t="inlineStr">
+        <is>
           <t>13,92%</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
-        <is>
-          <t>176</t>
-        </is>
-      </c>
-      <c r="K19" s="2" t="inlineStr">
-        <is>
-          <t>98290</t>
-        </is>
-      </c>
-      <c r="L19" s="2" t="inlineStr">
-        <is>
-          <t>83174</t>
-        </is>
-      </c>
-      <c r="M19" s="2" t="inlineStr">
-        <is>
-          <t>112806</t>
-        </is>
-      </c>
-      <c r="N19" s="2" t="inlineStr">
-        <is>
-          <t>13,21%</t>
-        </is>
-      </c>
-      <c r="O19" s="2" t="inlineStr">
-        <is>
-          <t>11,18%</t>
-        </is>
-      </c>
-      <c r="P19" s="2" t="inlineStr">
-        <is>
-          <t>15,16%</t>
-        </is>
-      </c>
-      <c r="Q19" s="2" t="inlineStr">
-        <is>
-          <t>186</t>
-        </is>
-      </c>
-      <c r="R19" s="2" t="inlineStr">
-        <is>
-          <t>114426</t>
-        </is>
-      </c>
-      <c r="S19" s="2" t="inlineStr">
-        <is>
-          <t>97691</t>
-        </is>
-      </c>
-      <c r="T19" s="2" t="inlineStr">
-        <is>
-          <t>135262</t>
-        </is>
-      </c>
-      <c r="U19" s="2" t="inlineStr">
-        <is>
-          <t>11,72%</t>
-        </is>
-      </c>
-      <c r="V19" s="2" t="inlineStr">
-        <is>
-          <t>10,01%</t>
-        </is>
-      </c>
-      <c r="W19" s="2" t="inlineStr">
-        <is>
-          <t>13,86%</t>
         </is>
       </c>
     </row>
@@ -10461,102 +10461,102 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>215980</t>
+          <t>208524</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>199794</t>
+          <t>192473</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>225386</t>
+          <t>216898</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>93,05%</t>
+          <t>92,85%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
+          <t>85,7%</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>96,58%</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
+          <t>951</t>
+        </is>
+      </c>
+      <c r="K20" s="2" t="inlineStr">
+        <is>
+          <t>711842</t>
+        </is>
+      </c>
+      <c r="L20" s="2" t="inlineStr">
+        <is>
+          <t>693954</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="inlineStr">
+        <is>
+          <t>726879</t>
+        </is>
+      </c>
+      <c r="N20" s="2" t="inlineStr">
+        <is>
+          <t>86,94%</t>
+        </is>
+      </c>
+      <c r="O20" s="2" t="inlineStr">
+        <is>
+          <t>84,76%</t>
+        </is>
+      </c>
+      <c r="P20" s="2" t="inlineStr">
+        <is>
+          <t>88,78%</t>
+        </is>
+      </c>
+      <c r="Q20" s="2" t="inlineStr">
+        <is>
+          <t>1045</t>
+        </is>
+      </c>
+      <c r="R20" s="2" t="inlineStr">
+        <is>
+          <t>920367</t>
+        </is>
+      </c>
+      <c r="S20" s="2" t="inlineStr">
+        <is>
+          <t>898115</t>
+        </is>
+      </c>
+      <c r="T20" s="2" t="inlineStr">
+        <is>
+          <t>939407</t>
+        </is>
+      </c>
+      <c r="U20" s="2" t="inlineStr">
+        <is>
+          <t>88,21%</t>
+        </is>
+      </c>
+      <c r="V20" s="2" t="inlineStr">
+        <is>
           <t>86,08%</t>
         </is>
       </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>97,1%</t>
-        </is>
-      </c>
-      <c r="J20" s="2" t="inlineStr">
-        <is>
-          <t>951</t>
-        </is>
-      </c>
-      <c r="K20" s="2" t="inlineStr">
-        <is>
-          <t>645620</t>
-        </is>
-      </c>
-      <c r="L20" s="2" t="inlineStr">
-        <is>
-          <t>631104</t>
-        </is>
-      </c>
-      <c r="M20" s="2" t="inlineStr">
-        <is>
-          <t>660736</t>
-        </is>
-      </c>
-      <c r="N20" s="2" t="inlineStr">
-        <is>
-          <t>86,79%</t>
-        </is>
-      </c>
-      <c r="O20" s="2" t="inlineStr">
-        <is>
-          <t>84,84%</t>
-        </is>
-      </c>
-      <c r="P20" s="2" t="inlineStr">
-        <is>
-          <t>88,82%</t>
-        </is>
-      </c>
-      <c r="Q20" s="2" t="inlineStr">
-        <is>
-          <t>1045</t>
-        </is>
-      </c>
-      <c r="R20" s="2" t="inlineStr">
-        <is>
-          <t>861600</t>
-        </is>
-      </c>
-      <c r="S20" s="2" t="inlineStr">
-        <is>
-          <t>840764</t>
-        </is>
-      </c>
-      <c r="T20" s="2" t="inlineStr">
-        <is>
-          <t>878335</t>
-        </is>
-      </c>
-      <c r="U20" s="2" t="inlineStr">
-        <is>
-          <t>88,28%</t>
-        </is>
-      </c>
-      <c r="V20" s="2" t="inlineStr">
-        <is>
-          <t>86,14%</t>
-        </is>
-      </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>89,99%</t>
+          <t>90,04%</t>
         </is>
       </c>
     </row>
@@ -10574,17 +10574,17 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>232116</t>
+          <t>224588</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>232116</t>
+          <t>224588</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>232116</t>
+          <t>224588</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -10609,17 +10609,17 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>743910</t>
+          <t>818742</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>743910</t>
+          <t>818742</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>743910</t>
+          <t>818742</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -10644,17 +10644,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>976026</t>
+          <t>1043331</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>976026</t>
+          <t>1043331</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>976026</t>
+          <t>1043331</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -10691,32 +10691,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>467564</t>
+          <t>538351</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>374078</t>
+          <t>496477</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>524262</t>
+          <t>584016</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>14,27%</t>
+          <t>16,24%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>11,42%</t>
+          <t>14,98%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>16,0%</t>
+          <t>17,62%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -10726,32 +10726,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>368389</t>
+          <t>405976</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>298303</t>
+          <t>374831</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>408664</t>
+          <t>434444</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>10,52%</t>
+          <t>11,49%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>8,52%</t>
+          <t>10,61%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>11,68%</t>
+          <t>12,3%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -10761,32 +10761,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>835953</t>
+          <t>944327</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>730355</t>
+          <t>890507</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>915276</t>
+          <t>1000418</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>12,34%</t>
+          <t>13,79%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>10,78%</t>
+          <t>13,0%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>13,51%</t>
+          <t>14,61%</t>
         </is>
       </c>
     </row>
@@ -10804,32 +10804,32 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>2809183</t>
+          <t>2776245</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>2752485</t>
+          <t>2730580</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>2902669</t>
+          <t>2818119</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>85,73%</t>
+          <t>83,76%</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>84,0%</t>
+          <t>82,38%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>88,58%</t>
+          <t>85,02%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -10839,32 +10839,32 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>3131870</t>
+          <t>3127142</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>3091595</t>
+          <t>3098674</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>3201956</t>
+          <t>3158287</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>89,48%</t>
+          <t>88,51%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>88,32%</t>
+          <t>87,7%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>91,48%</t>
+          <t>89,39%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -10874,32 +10874,32 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>5941053</t>
+          <t>5903387</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>5861730</t>
+          <t>5847296</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>6046651</t>
+          <t>5957207</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>87,66%</t>
+          <t>86,21%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>86,49%</t>
+          <t>85,39%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>89,22%</t>
+          <t>87,0%</t>
         </is>
       </c>
     </row>
@@ -10917,17 +10917,17 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>3276747</t>
+          <t>3314596</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>3276747</t>
+          <t>3314596</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>3276747</t>
+          <t>3314596</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -10952,17 +10952,17 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>3500259</t>
+          <t>3533118</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>3500259</t>
+          <t>3533118</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>3500259</t>
+          <t>3533118</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -10987,17 +10987,17 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>6777006</t>
+          <t>6847714</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>6777006</t>
+          <t>6847714</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>6777006</t>
+          <t>6847714</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
